--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Passive Strategy Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Passive Strategy Fund (FOF).xlsx
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Passive Strategy Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,22 +70,28 @@
     <t>INF109KC15I8</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Healthcare ETF</t>
+  </si>
+  <si>
+    <t>INF109KC1Q72</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Nifty India Consumption ETF</t>
+  </si>
+  <si>
+    <t>INF109KC1V42</t>
+  </si>
+  <si>
     <t>ICICI Prudential Nifty FMCG ETF</t>
   </si>
   <si>
     <t>INF109KC19V3</t>
   </si>
   <si>
-    <t>ICICI Prudential Nifty India Consumption ETF</t>
-  </si>
-  <si>
-    <t>INF109KC1V42</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Nifty Healthcare ETF</t>
-  </si>
-  <si>
-    <t>INF109KC1Q72</t>
+    <t>ICICI Prudential Nifty IT ETF</t>
+  </si>
+  <si>
+    <t>INF109KC16I6</t>
   </si>
   <si>
     <t>ICICI Prudential Nifty Oil &amp; Gas ETF</t>
@@ -94,12 +100,6 @@
     <t>INF109KC18W3</t>
   </si>
   <si>
-    <t>ICICI Prudential Nifty IT ETF</t>
-  </si>
-  <si>
-    <t>INF109KC16I6</t>
-  </si>
-  <si>
     <t>ICICI Prudential Nifty Infrastructure ETF</t>
   </si>
   <si>
@@ -112,18 +112,18 @@
     <t>INF109KC19O8</t>
   </si>
   <si>
+    <t>ICICI Prudential Nifty Auto ETF</t>
+  </si>
+  <si>
+    <t>INF109KC10V2</t>
+  </si>
+  <si>
     <t>Reliance CPSE ETF</t>
   </si>
   <si>
     <t>INF457M01133</t>
   </si>
   <si>
-    <t>BHARAT 22 ETF</t>
-  </si>
-  <si>
-    <t>INF109KB15Y7</t>
-  </si>
-  <si>
     <t>ICICI Prudential Nifty Metal ETF</t>
   </si>
   <si>
@@ -145,7 +145,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -951,10 +951,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>16757.81</v>
+        <v>19144.76</v>
       </c>
       <c r="G5" s="10">
-        <v>0.967177083504</v>
+        <v>0.9860746398774</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -974,13 +974,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>14193963</v>
+        <v>14195963</v>
       </c>
       <c r="F6" s="15">
-        <v>3478.94</v>
+        <v>3919.51</v>
       </c>
       <c r="G6" s="16">
-        <v>0.2007870385741</v>
+        <v>0.2018792302305</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -1000,13 +1000,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="14">
-        <v>5929440</v>
+        <v>5690440</v>
       </c>
       <c r="F7" s="15">
-        <v>2987.84</v>
+        <v>3222.50</v>
       </c>
       <c r="G7" s="16">
-        <v>0.1724431997485</v>
+        <v>0.1659788645565</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -1026,13 +1026,13 @@
         <v>15</v>
       </c>
       <c r="E8" s="14">
-        <v>3156300</v>
+        <v>1339801</v>
       </c>
       <c r="F8" s="15">
-        <v>1875.47</v>
+        <v>1903.05</v>
       </c>
       <c r="G8" s="16">
-        <v>0.108242759931</v>
+        <v>0.0980189536677</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -1055,10 +1055,10 @@
         <v>1450930</v>
       </c>
       <c r="F9" s="15">
-        <v>1647.82</v>
+        <v>1699.18</v>
       </c>
       <c r="G9" s="16">
-        <v>0.095103939103</v>
+        <v>0.0875183761294</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>12</v>
@@ -1078,13 +1078,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="14">
-        <v>1136801</v>
+        <v>2840300</v>
       </c>
       <c r="F10" s="15">
-        <v>1599.25</v>
+        <v>1672.08</v>
       </c>
       <c r="G10" s="16">
-        <v>0.092300721323</v>
+        <v>0.0861225569736</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>12</v>
@@ -1104,13 +1104,13 @@
         <v>15</v>
       </c>
       <c r="E11" s="14">
-        <v>12876960</v>
+        <v>3941290</v>
       </c>
       <c r="F11" s="15">
-        <v>1368.82</v>
+        <v>1591.89</v>
       </c>
       <c r="G11" s="16">
-        <v>0.0790014527818</v>
+        <v>0.0819922714348</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>12</v>
@@ -1130,13 +1130,13 @@
         <v>15</v>
       </c>
       <c r="E12" s="14">
-        <v>2634290</v>
+        <v>12976960</v>
       </c>
       <c r="F12" s="15">
-        <v>1210.19</v>
+        <v>1488.46</v>
       </c>
       <c r="G12" s="16">
-        <v>0.0698461215807</v>
+        <v>0.076664980834</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>12</v>
@@ -1156,13 +1156,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="14">
-        <v>1068642</v>
+        <v>1601642</v>
       </c>
       <c r="F13" s="15">
-        <v>919.67</v>
+        <v>1470.15</v>
       </c>
       <c r="G13" s="16">
-        <v>0.0530787584049</v>
+        <v>0.0757219015446</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>12</v>
@@ -1182,13 +1182,13 @@
         <v>15</v>
       </c>
       <c r="E14" s="14">
-        <v>820000</v>
+        <v>778000</v>
       </c>
       <c r="F14" s="15">
-        <v>670.51</v>
+        <v>675.85</v>
       </c>
       <c r="G14" s="16">
-        <v>0.0386984878251</v>
+        <v>0.0348104935951</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>12</v>
@@ -1208,13 +1208,13 @@
         <v>15</v>
       </c>
       <c r="E15" s="14">
-        <v>758200</v>
+        <v>2463500</v>
       </c>
       <c r="F15" s="15">
-        <v>655.77</v>
+        <v>587.79</v>
       </c>
       <c r="G15" s="16">
-        <v>0.0378477686553</v>
+        <v>0.0302748539325</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>12</v>
@@ -1234,13 +1234,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="14">
-        <v>165000</v>
+        <v>574200</v>
       </c>
       <c r="F16" s="15">
-        <v>172.90</v>
+        <v>525.74</v>
       </c>
       <c r="G16" s="16">
-        <v>0.0099789243187</v>
+        <v>0.027078891622</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>12</v>
@@ -1260,13 +1260,13 @@
         <v>15</v>
       </c>
       <c r="E17" s="14">
-        <v>2026493</v>
+        <v>4223493</v>
       </c>
       <c r="F17" s="15">
-        <v>170.63</v>
+        <v>388.56</v>
       </c>
       <c r="G17" s="16">
-        <v>0.0098479112579</v>
+        <v>0.0200132653567</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>12</v>
@@ -1297,10 +1297,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="9">
-        <v>403.35</v>
+        <v>276.12</v>
       </c>
       <c r="G19" s="10">
-        <v>0.02327934716</v>
+        <v>0.0142219035163</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>12</v>
@@ -1331,10 +1331,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="18">
-        <v>165.3568145600002</v>
+        <v>-5.757426350002788</v>
       </c>
       <c r="G21" s="19">
-        <v>0.009543569335358035</v>
+        <v>-0.00029654339436500427</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>12</v>
@@ -1357,10 +1357,10 @@
         <v>12</v>
       </c>
       <c r="F22" s="18">
-        <v>17326.51681456</v>
+        <v>19415.12257365</v>
       </c>
       <c r="G22" s="19">
-        <v>0.9999999999993581</v>
+        <v>0.9999999999993349</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>12</v>
